--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484679_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484679_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.631</v>
+        <v>3.8011</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1541</v>
+        <v>5.4976</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5231</v>
+        <v>-1.6965</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0693</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4633</v>
+        <v>-0.2932</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.46</v>
+        <v>-0.1165</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0033</v>
+        <v>-0.1767</v>
       </c>
       <c r="V2" t="n">
         <v>5.8966</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.941</v>
+        <v>2.5496</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4396</v>
+        <v>2.6862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5014</v>
+        <v>-0.1366</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2791</v>
+        <v>0.0244</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2696</v>
+        <v>-1.1491</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0095</v>
+        <v>1.1735</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7631</v>
+        <v>0.1497</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3625</v>
+        <v>0.13</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5994</v>
+        <v>0.0197</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.484</v>
+        <v>-0.1253</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0929</v>
+        <v>-1.2792</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6089</v>
+        <v>1.1538</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3665</v>
+        <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2117</v>
+        <v>0.9204</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5928</v>
+        <v>0.8088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6189</v>
+        <v>0.1116</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2552</v>
+        <v>1.7099</v>
       </c>
       <c r="E4" t="n">
-        <v>2.59</v>
+        <v>1.3819</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3348</v>
+        <v>0.328</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0244</v>
+        <v>1.2791</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1491</v>
+        <v>1.2696</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1735</v>
+        <v>0.0095</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1497</v>
+        <v>1.7631</v>
       </c>
       <c r="K4" t="n">
-        <v>0.13</v>
+        <v>2.3625</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0197</v>
+        <v>-0.5994</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1253</v>
+        <v>-0.484</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2792</v>
+        <v>-1.0929</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1538</v>
+        <v>0.6089</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6261</v>
+        <v>0.9806</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7127</v>
+        <v>0.5351</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0866</v>
+        <v>0.4455</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>I. EGIDO MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7594</v>
+        <v>0.6502</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1131</v>
+        <v>0.6502</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3537</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4355</v>
+        <v>0.6502</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6576</v>
+        <v>0.6502</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0931</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2067</v>
+        <v>0.6502</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1392</v>
+        <v>0.6502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2288</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7968</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0256</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9128</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5008</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. EGIDO MUÑOZ</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6502</v>
+        <v>0.2346</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6502</v>
+        <v>0.6874</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.4528</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6502</v>
+        <v>0.4355</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502</v>
+        <v>-0.6576</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.0931</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6502</v>
+        <v>0.2067</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6502</v>
+        <v>0.1392</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.2288</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.7968</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.0256</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.388</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.0751</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4252</v>
+        <v>-0.1035</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2672</v>
+        <v>-0.0199</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1579</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1889</v>
@@ -1078,13 +1078,13 @@
         <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>0.214</v>
+        <v>0.5356</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2368</v>
+        <v>0.4842</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0229</v>
+        <v>0.0515</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7899</v>
+        <v>-0.2893</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7387</v>
+        <v>-1.4363</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9488</v>
+        <v>1.147</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5344</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.5958</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1818</v>
+        <v>0.4842</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0866</v>
+        <v>0.1116</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8852</v>
+        <v>-0.6845</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1802</v>
+        <v>-1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>0.295</v>
+        <v>0.3446</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3701</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4617</v>
+        <v>-0.2609</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3122</v>
+        <v>-0.161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V10" t="n">
         <v>0.4964</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6028</v>
+        <v>-1.6772</v>
       </c>
       <c r="E11" t="n">
         <v>-0.7845</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8183</v>
+        <v>-0.8927</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3233</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0126</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1526</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4128</v>
+        <v>-2.3489</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5743</v>
+        <v>-1.5095</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8385</v>
+        <v>-0.8394</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5612</v>
+        <v>-0.2434</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.609</v>
+        <v>0.3464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.5898</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0177</v>
+        <v>-0.4401</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4184</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5994</v>
+        <v>-1.1987</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5434</v>
+        <v>0.1967</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1907</v>
+        <v>-0.4122</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3528</v>
+        <v>0.6089</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9163</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0158</v>
+        <v>-2.7489</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1919</v>
+        <v>0.092</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1297</v>
+        <v>0.0905</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0622</v>
+        <v>0.0015</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2566</v>
+        <v>0.1848</v>
       </c>
       <c r="W12" t="n">
         <v>1.5889</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3324</v>
+        <v>-1.4041</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6022</v>
+        <v>-2.5778</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5646</v>
+        <v>-1.6154</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0376</v>
+        <v>-0.9624</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2434</v>
+        <v>-2.5612</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3464</v>
+        <v>-1.609</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5898</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4401</v>
+        <v>-1.0177</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.4184</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1987</v>
+        <v>-0.5994</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1967</v>
+        <v>-1.5434</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4122</v>
+        <v>-1.1907</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6089</v>
+        <v>-0.3528</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3823</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7489</v>
+        <v>-2.0158</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1612</v>
+        <v>-0.3569</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0355</v>
+        <v>-0.1708</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1967</v>
+        <v>-0.1861</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1848</v>
+        <v>1.2566</v>
       </c>
       <c r="W13" t="n">
         <v>1.5889</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4041</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6121</v>
+        <v>-6.2963</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0247</v>
+        <v>-3.585</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5874</v>
+        <v>-2.7113</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8929</v>
@@ -1546,13 +1546,13 @@
         <v>0.1833</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8149</v>
+        <v>-0.4991</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7157</v>
+        <v>-0.276</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0992</v>
+        <v>-0.2231</v>
       </c>
       <c r="V14" t="n">
         <v>-2.3387</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.223</v>
+        <v>-6.7338</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.8478</v>
+        <v>-5.4082</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3751</v>
+        <v>-1.3256</v>
       </c>
       <c r="G15" t="n">
         <v>-5.8881</v>
@@ -1624,13 +1624,13 @@
         <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4805</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2036</v>
+        <v>0.2361</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2769</v>
+        <v>-0.2274</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4041</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.0662</v>
+        <v>-10.5157</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.784799999999999</v>
+        <v>-3.234300000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.2812</v>
+        <v>-7.2813</v>
       </c>
       <c r="G16" t="n">
         <v>-11.4322</v>
@@ -1684,13 +1684,13 @@
         <v>-11.6978</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.7336</v>
+        <v>-5.733599999999999</v>
       </c>
       <c r="N16" t="n">
         <v>-9.098000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.364100000000001</v>
+        <v>3.3641</v>
       </c>
       <c r="P16" t="n">
         <v>-3.6651</v>
@@ -1702,16 +1702,16 @@
         <v>10.9954</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4737</v>
+        <v>3.024100000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>2.274</v>
+        <v>2.8245</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1996</v>
+        <v>0.1997000000000002</v>
       </c>
       <c r="V16" t="n">
-        <v>1.557600000000002</v>
+        <v>1.557600000000001</v>
       </c>
       <c r="W16" t="n">
         <v>14.3002</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.0475</v>
+        <v>6.0888</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6302</v>
+        <v>3.861</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4173</v>
+        <v>2.2278</v>
       </c>
       <c r="G17" t="n">
         <v>3.4047</v>
@@ -1780,13 +1780,13 @@
         <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8656</v>
+        <v>0.9069</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1328</v>
+        <v>0.3635</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7328</v>
+        <v>0.5433</v>
       </c>
       <c r="V17" t="n">
         <v>2.8767</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1028</v>
+        <v>4.6066</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0487</v>
+        <v>2.7834</v>
       </c>
       <c r="F18" t="n">
-        <v>2.054</v>
+        <v>1.8232</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2067</v>
+        <v>2.0586</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2131</v>
+        <v>-0.2523</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4198</v>
+        <v>2.3109</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1133</v>
+        <v>1.4697</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.155</v>
+        <v>0.7613</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>0.7085</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3201</v>
+        <v>0.5888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0581</v>
+        <v>-1.0136</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3781</v>
+        <v>1.6024</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6132</v>
+        <v>-0.2242</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5181</v>
+        <v>0.1908</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0951</v>
+        <v>-0.415</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6439</v>
+        <v>2.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4905</v>
+        <v>4.372</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5792</v>
+        <v>4.06</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0887</v>
+        <v>0.312</v>
       </c>
       <c r="G19" t="n">
         <v>3.8007</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6871</v>
+        <v>-0.8056</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7157</v>
+        <v>-0.2349</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9714</v>
+        <v>-0.5707</v>
       </c>
       <c r="V19" t="n">
         <v>0.6439</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1948</v>
+        <v>2.828</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8219</v>
+        <v>0.7987</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3729</v>
+        <v>2.0293</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0586</v>
+        <v>1.2067</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2523</v>
+        <v>-0.2131</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3109</v>
+        <v>1.4198</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4697</v>
+        <v>-0.1133</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7613</v>
+        <v>-0.155</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7085</v>
+        <v>0.0417</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5888</v>
+        <v>1.3201</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0136</v>
+        <v>-0.0581</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6024</v>
+        <v>1.3781</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.636</v>
+        <v>0.3384</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.2681</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8652</v>
+        <v>0.0703</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2224</v>
+        <v>0.6439</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.548</v>
+        <v>1.918</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7609</v>
+        <v>-1.5686</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3089</v>
+        <v>3.4866</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4747</v>
@@ -2092,13 +2092,13 @@
         <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>0.033</v>
+        <v>0.4031</v>
       </c>
       <c r="T21" t="n">
-        <v>0.126</v>
+        <v>0.3183</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0929</v>
+        <v>0.0848</v>
       </c>
       <c r="V21" t="n">
         <v>1.89</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.121</v>
+        <v>0.968</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5305</v>
+        <v>2.1459</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4095</v>
+        <v>-1.1779</v>
       </c>
       <c r="G22" t="n">
         <v>3.4066</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3869</v>
+        <v>0.234</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6765</v>
+        <v>0.2919</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2895</v>
+        <v>-0.0579</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8559</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>A. SANCHEZ DE LA IGLESIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0979</v>
+        <v>0.2125</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3567</v>
+        <v>-0.7985</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4546</v>
+        <v>1.011</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6807</v>
+        <v>0.1895</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1679</v>
+        <v>0.3178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5128</v>
+        <v>-0.1282</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.6194</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6807</v>
+        <v>0.8089</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1679</v>
+        <v>0.2961</v>
       </c>
       <c r="O23" t="n">
         <v>0.5128</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3995</v>
+        <v>-0.1603</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4404</v>
+        <v>-0.1791</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0409</v>
+        <v>0.0188</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SANCHEZ DE LA IGLESIA</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0118</v>
+        <v>0.1766</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8946</v>
+        <v>-1.3567</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8828</v>
+        <v>1.5333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1895</v>
+        <v>0.6807</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3178</v>
+        <v>0.1679</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1282</v>
+        <v>0.5128</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6194</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.641</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8089</v>
+        <v>0.6807</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2961</v>
+        <v>0.1679</v>
       </c>
       <c r="O24" t="n">
         <v>0.5128</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3846</v>
+        <v>-0.3209</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2753</v>
+        <v>-0.4404</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1094</v>
+        <v>0.1195</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8092</v>
+        <v>-1.713</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="F25" t="n">
         <v>-1.5339</v>
@@ -2404,10 +2404,10 @@
         <v>0.3665</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4505</v>
+        <v>-2.0114</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2061</v>
+        <v>-0.8413</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2444</v>
+        <v>-1.1701</v>
       </c>
       <c r="G26" t="n">
-        <v>0.251</v>
+        <v>-0.2254</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1208</v>
+        <v>0.3196</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3719</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.2403</v>
+        <v>-0.2726</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1888</v>
+        <v>0.3685</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0515</v>
+        <v>-0.641</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9893</v>
+        <v>0.0472</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3097</v>
+        <v>-0.0489</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3204</v>
+        <v>0.0961</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0681</v>
+        <v>-0.1239</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8808</v>
+        <v>0.0543</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1873</v>
+        <v>-0.1782</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.267</v>
+        <v>-2.212</v>
       </c>
       <c r="W26" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.5339</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.5199</v>
+        <v>-2.3355</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.2259</v>
+        <v>0.0824</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.294</v>
+        <v>-2.4179</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2254</v>
+        <v>0.251</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3196</v>
+        <v>-0.1208</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5449000000000001</v>
+        <v>0.3719</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2726</v>
+        <v>1.2403</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3685</v>
+        <v>1.1888</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.641</v>
+        <v>0.0515</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0472</v>
+        <v>-0.9893</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0489</v>
+        <v>-1.3097</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0961</v>
+        <v>0.3204</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6323</v>
+        <v>-0.953</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3303</v>
+        <v>-0.5924</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.302</v>
+        <v>-0.3607</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.212</v>
+        <v>-1.267</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.6231</v>
+        <v>1.267</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.7449</v>
+        <v>-2.7623</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6097</v>
+        <v>-1.7058</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1352</v>
+        <v>-1.0565</v>
       </c>
       <c r="G28" t="n">
         <v>-1.233</v>
@@ -2638,13 +2638,13 @@
         <v>0.5498</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.2894</v>
+        <v>-0.3069</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0355</v>
+        <v>-0.0607</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3249</v>
+        <v>-0.2462</v>
       </c>
       <c r="V28" t="n">
         <v>-1.5889</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>11.0662</v>
+        <v>12.34829999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>7.281300000000003</v>
+        <v>7.2814</v>
       </c>
       <c r="F29" t="n">
-        <v>3.7848</v>
+        <v>5.066900000000002</v>
       </c>
       <c r="G29" t="n">
         <v>11.4319</v>
@@ -2686,13 +2686,13 @@
         <v>3.0991</v>
       </c>
       <c r="I29" t="n">
-        <v>8.333499999999999</v>
+        <v>8.333499999999997</v>
       </c>
       <c r="J29" t="n">
-        <v>5.733799999999999</v>
+        <v>5.7338</v>
       </c>
       <c r="K29" t="n">
-        <v>9.098100000000001</v>
+        <v>9.098100000000002</v>
       </c>
       <c r="L29" t="n">
         <v>-3.3642</v>
@@ -2716,13 +2716,13 @@
         <v>14.6607</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.473600000000001</v>
+        <v>-1.1915</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.1996000000000001</v>
+        <v>-0.1997</v>
       </c>
       <c r="U29" t="n">
-        <v>-2.2738</v>
+        <v>-0.9919999999999999</v>
       </c>
       <c r="V29" t="n">
         <v>-1.5578</v>
